--- a/261/food/kp2026.xlsx
+++ b/261/food/kp2026.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B1" s="26" t="inlineStr">
         <is>
-          <t>ГБОУ С(к)ОШИ для детей с ЗПР</t>
+          <t xml:space="preserve">ГБОУ С(к)ОШИ для детей с ЗПР </t>
         </is>
       </c>
       <c r="C1" s="28" t="n"/>
@@ -655,8 +655,10 @@
           <t>Год</t>
         </is>
       </c>
-      <c r="AD1" s="27" t="n">
-        <v>2026</v>
+      <c r="AD1" s="27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="AE1" s="29" t="n"/>
       <c r="AF1" s="1" t="n"/>
